--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsB2cDeclareReconciliation.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsB2cDeclareReconciliation.xlsx
@@ -76,7 +76,7 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.approveStatus}</t>
+    <t>{.approveStatusName}</t>
   </si>
   <si>
     <t>{.cycle}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsB2cDeclareReconciliation.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsB2cDeclareReconciliation.xlsx
@@ -100,7 +100,7 @@
     <t>{.actualWeightUnit}</t>
   </si>
   <si>
-    <t>{.currency}</t>
+    <t>{.currencyName}</t>
   </si>
   <si>
     <t>{.reconciliationDate}</t>
